--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/UTAH_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/UTAH_2011.xlsx
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C108">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C174">
@@ -8743,7 +8743,7 @@
         <v>140</v>
       </c>
       <c r="D466">
-        <v>0.009556313993174</v>
+        <v>0.009556313993174002</v>
       </c>
     </row>
     <row r="467">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C659">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C962">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="B1052" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1052">
@@ -19327,7 +19327,7 @@
         <v>134</v>
       </c>
       <c r="D1054">
-        <v>0.009146757679181</v>
+        <v>0.009146757679181002</v>
       </c>
     </row>
     <row r="1055">
